--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368432</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210293</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790932</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848037</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403181</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75729871</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75729872</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403213</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368292</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129027271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129027295</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857914</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151855</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151813</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2502,8 +2587,32 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88456159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88403181</v>
+        <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>96458</v>
+        <v>95939</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,34 +1395,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>2412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blackstahyttan, skog V om - nära Gretefallet, Nrk</t>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499573</v>
+        <v>499535</v>
       </c>
       <c r="R8" t="n">
-        <v>6580919</v>
+        <v>6580888</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,12 +1453,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,38 +1467,48 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88403181</t>
+          <t>https://artportalen.se/Sighting/136103735</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75729871</v>
+        <v>88403181</v>
       </c>
       <c r="B9" t="n">
-        <v>91680</v>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,34 +1516,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blackstahyttan NV, Nrk</t>
+          <t>Blackstahyttan, skog V om - nära Gretefallet, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499522</v>
+        <v>499573</v>
       </c>
       <c r="R9" t="n">
-        <v>6580929</v>
+        <v>6580919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,12 +1570,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-11-16</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-11-16</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,28 +1586,33 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Tverling, Lotta Sörman</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75729871</t>
+          <t>https://artportalen.se/Sighting/88403181</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75729872</v>
+        <v>75729871</v>
       </c>
       <c r="B10" t="n">
         <v>91680</v>
@@ -1628,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499540</v>
+        <v>499522</v>
       </c>
       <c r="R10" t="n">
-        <v>6580911</v>
+        <v>6580929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,13 +1708,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75729872</t>
+          <t>https://artportalen.se/Sighting/75729871</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88403213</v>
+        <v>75729872</v>
       </c>
       <c r="B11" t="n">
         <v>91680</v>
@@ -1726,14 +1745,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blackstahyttan, skog V om, Nrk</t>
+          <t>Blackstahyttan NV, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499527</v>
+        <v>499540</v>
       </c>
       <c r="R11" t="n">
-        <v>6580895</v>
+        <v>6580911</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,12 +1779,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
+          <t>2018-11-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
+          <t>2018-11-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,33 +1795,28 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>blandskog, delvis översilad</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>David Tverling, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88403213</t>
+          <t>https://artportalen.se/Sighting/75729872</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96368292</v>
+        <v>88403213</v>
       </c>
       <c r="B12" t="n">
         <v>91680</v>
@@ -1833,14 +1847,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, skog V om, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499544</v>
+        <v>499527</v>
       </c>
       <c r="R12" t="n">
-        <v>6580892</v>
+        <v>6580895</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,12 +1881,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,7 +1900,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>blandskog, delvis översilad</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1900,20 +1914,16 @@
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368292</t>
+          <t>https://artportalen.se/Sighting/88403213</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129027271</v>
+        <v>96368292</v>
       </c>
       <c r="B13" t="n">
         <v>91680</v>
@@ -1941,34 +1951,20 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Alvars stig, Alvars stig, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>499544</v>
       </c>
       <c r="R13" t="n">
-        <v>6580887</v>
+        <v>6580892</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,22 +1988,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,32 +2005,36 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129027271</t>
+          <t>https://artportalen.se/Sighting/96368292</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129027295</v>
+        <v>129027271</v>
       </c>
       <c r="B14" t="n">
         <v>91680</v>
@@ -2072,17 +2062,31 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gretefallet, Gretefallet, Nrk</t>
+          <t>Alvars stig, Alvars stig, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499656</v>
+        <v>499544</v>
       </c>
       <c r="R14" t="n">
-        <v>6580958</v>
+        <v>6580887</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,6 +2139,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2150,57 +2159,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129027295</t>
+          <t>https://artportalen.se/Sighting/129027271</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111857914</v>
+        <v>129027295</v>
       </c>
       <c r="B15" t="n">
-        <v>93189</v>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Gretefallet, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499548</v>
+        <v>499656</v>
       </c>
       <c r="R15" t="n">
-        <v>6580904</v>
+        <v>6580958</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2224,12 +2230,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,72 +2254,74 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111857914</t>
+          <t>https://artportalen.se/Sighting/129027295</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88151855</v>
+        <v>111857914</v>
       </c>
       <c r="B16" t="n">
-        <v>106813</v>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499545</v>
+        <v>499548</v>
       </c>
       <c r="R16" t="n">
-        <v>6581051</v>
+        <v>6580904</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2327,12 +2345,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,42 +2359,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151855</t>
+          <t>https://artportalen.se/Sighting/111857914</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>88151813</v>
+        <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>99210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,37 +2394,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499545</v>
+        <v>499535</v>
       </c>
       <c r="R17" t="n">
-        <v>6581051</v>
+        <v>6580888</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,12 +2456,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,42 +2470,39 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151813</t>
+          <t>https://artportalen.se/Sighting/136103719</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>88456159</v>
+        <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>108317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,34 +2510,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499493</v>
+        <v>499535</v>
       </c>
       <c r="R18" t="n">
-        <v>6581024</v>
+        <v>6580888</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,12 +2568,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,33 +2582,1043 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>fuktig granskog</t>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136103713</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>88151855</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499545</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6581051</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151855</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136103760</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98155</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499535</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6580888</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136103760</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136107235</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100054</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499528</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6580884</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136107235</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136103740</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100318</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>499535</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6580888</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136103740</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136107228</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100318</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499528</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6580884</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136107228</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>88151813</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499545</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6581051</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151813</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>88456159</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>499493</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6581024</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/88456159</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136103729</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100905</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499535</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6580888</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136103729</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136103710</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499535</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6580888</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136103710</t>
         </is>
       </c>
     </row>
@@ -2612,6 +3641,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95939</v>
+        <v>95940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100054</v>
+        <v>100056</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100318</v>
+        <v>100320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100318</v>
+        <v>100320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100905</v>
+        <v>100907</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100056</v>
+        <v>100057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100320</v>
+        <v>100321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100320</v>
+        <v>100321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100907</v>
+        <v>100908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100057</v>
+        <v>100058</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100321</v>
+        <v>100322</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100321</v>
+        <v>100322</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100908</v>
+        <v>100909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95942</v>
+        <v>95948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100058</v>
+        <v>100064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100322</v>
+        <v>100328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100322</v>
+        <v>100328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100909</v>
+        <v>100915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95948</v>
+        <v>95949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100064</v>
+        <v>100065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100328</v>
+        <v>100329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100328</v>
+        <v>100329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100915</v>
+        <v>100916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
